--- a/artfynd/A 47807-2023 artfynd.xlsx
+++ b/artfynd/A 47807-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 47807-2023 artfynd.xlsx
+++ b/artfynd/A 47807-2023 artfynd.xlsx
@@ -801,11 +801,11 @@
         <v>114057126</v>
       </c>
       <c r="B3" t="n">
-        <v>56470</v>
+        <v>56585</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">

--- a/artfynd/A 47807-2023 artfynd.xlsx
+++ b/artfynd/A 47807-2023 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>114057126</v>
       </c>
       <c r="B3" t="n">
-        <v>56585</v>
+        <v>56586</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 47807-2023 artfynd.xlsx
+++ b/artfynd/A 47807-2023 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>114057126</v>
       </c>
       <c r="B3" t="n">
-        <v>56586</v>
+        <v>56680</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
